--- a/ruoyi-modules/ruoyi-procurement/src/main/resources/templates/最终模板.xlsx
+++ b/ruoyi-modules/ruoyi-procurement/src/main/resources/templates/最终模板.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\工作\1.采购申请管理\26年\中心AI项目\（自购）采购+验收\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\jvkit\workspace\oa\ruoyi-6x\ruoyi-modules\ruoyi-procurement\src\main\resources\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3716D4DD-9B12-4D95-8A83-0DC65806C4C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03EC3F8A-430A-4C77-895F-923C77247DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5200" yWindow="3000" windowWidth="19200" windowHeight="11180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="139">
   <si>
     <t>申请人：</t>
   </si>
@@ -202,40 +202,13 @@
     </r>
   </si>
   <si>
-    <t>示例</t>
-  </si>
-  <si>
     <t>科研类</t>
   </si>
   <si>
     <t>100材料</t>
   </si>
   <si>
-    <t>101金属材料</t>
-  </si>
-  <si>
     <t>医用应用物理研发测试平台</t>
-  </si>
-  <si>
-    <t>锆</t>
-  </si>
-  <si>
-    <t>g</t>
-  </si>
-  <si>
-    <t>4N,粉末</t>
-  </si>
-  <si>
-    <t>中科言诺</t>
-  </si>
-  <si>
-    <t>张三</t>
-  </si>
-  <si>
-    <t>张三；李四；王五</t>
-  </si>
-  <si>
-    <t>金属平台合作项目-金属表面镀层；膜材原材料；......</t>
   </si>
   <si>
     <r>
@@ -1602,7 +1575,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1624,10 +1597,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1674,28 +1643,22 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="fill" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="fill" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="fill" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1709,16 +1672,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="fill" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1996,1027 +1949,981 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R28"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:R27"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.77734375" style="13" customWidth="1"/>
-    <col min="2" max="3" width="10" style="13" customWidth="1"/>
-    <col min="4" max="4" width="21.33203125" style="13" customWidth="1"/>
-    <col min="5" max="5" width="28.44140625" style="13" customWidth="1"/>
-    <col min="6" max="6" width="26.5546875" style="14" customWidth="1"/>
-    <col min="7" max="7" width="6.77734375" style="13" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" style="13" customWidth="1"/>
-    <col min="9" max="9" width="79.44140625" style="14" customWidth="1"/>
-    <col min="10" max="13" width="13.44140625" style="14" customWidth="1"/>
-    <col min="14" max="14" width="7.77734375" style="13" customWidth="1"/>
-    <col min="15" max="16" width="18.109375" style="14" customWidth="1"/>
-    <col min="17" max="17" width="62.77734375" style="14" customWidth="1"/>
-    <col min="18" max="18" width="18.5546875" style="15" customWidth="1"/>
-    <col min="19" max="16384" width="8.77734375" style="16"/>
+    <col min="1" max="1" width="5.75" style="12" customWidth="1"/>
+    <col min="2" max="3" width="10" style="12" customWidth="1"/>
+    <col min="4" max="4" width="21.33203125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="28.4140625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="26.58203125" style="13" customWidth="1"/>
+    <col min="7" max="7" width="6.75" style="12" customWidth="1"/>
+    <col min="8" max="8" width="14.75" style="12" customWidth="1"/>
+    <col min="9" max="9" width="79.4140625" style="13" customWidth="1"/>
+    <col min="10" max="13" width="13.4140625" style="13" customWidth="1"/>
+    <col min="14" max="14" width="7.75" style="12" customWidth="1"/>
+    <col min="15" max="16" width="18.08203125" style="13" customWidth="1"/>
+    <col min="17" max="17" width="62.75" style="13" customWidth="1"/>
+    <col min="18" max="18" width="18.58203125" style="14" customWidth="1"/>
+    <col min="19" max="16384" width="8.75" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="11" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:18" s="11" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="18"/>
+    </row>
+    <row r="2" spans="1:18" ht="32" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="19"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+    </row>
+    <row r="3" spans="1:18" ht="25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="21"/>
+      <c r="N3" s="15"/>
+      <c r="O3" s="21"/>
+      <c r="P3" s="21"/>
+      <c r="Q3" s="21"/>
+    </row>
+    <row r="4" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="35"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="21"/>
+      <c r="P4" s="21"/>
+      <c r="Q4" s="21"/>
+    </row>
+    <row r="5" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="22"/>
+      <c r="B5" s="36" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="36"/>
+      <c r="K5" s="36"/>
+      <c r="L5" s="36"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="29"/>
+      <c r="Q5" s="23"/>
+    </row>
+    <row r="6" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="15"/>
+      <c r="B6" s="36" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="36"/>
+      <c r="J6" s="36"/>
+      <c r="K6" s="36"/>
+      <c r="L6" s="36"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="29"/>
+      <c r="Q6" s="23"/>
+    </row>
+    <row r="7" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="K7" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="L7" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="M7" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="N7" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="O7" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="P7" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q7" s="26" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B8" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H8" s="12">
+        <v>2</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12">
+        <v>899</v>
+      </c>
+      <c r="L8" s="12">
+        <v>1798</v>
+      </c>
+      <c r="M8" s="12">
+        <v>1850</v>
+      </c>
+      <c r="N8" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="O8" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="P8" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q8" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="R8" s="28" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B9" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="H9" s="12">
+        <v>8</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12">
+        <v>500</v>
+      </c>
+      <c r="L9" s="12">
+        <v>4000</v>
+      </c>
+      <c r="M9" s="12">
+        <v>4100</v>
+      </c>
+      <c r="N9" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="O9" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="P9" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q9" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="R9" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="18"/>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="18"/>
-      <c r="R1" s="19"/>
-    </row>
-    <row r="2" spans="1:18" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="21"/>
-      <c r="N2" s="20"/>
-      <c r="O2" s="21"/>
-      <c r="P2" s="21"/>
-      <c r="Q2" s="21"/>
-    </row>
-    <row r="3" spans="1:18" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="22"/>
-      <c r="L3" s="22"/>
-      <c r="M3" s="22"/>
-      <c r="N3" s="16"/>
-      <c r="O3" s="22"/>
-      <c r="P3" s="22"/>
-      <c r="Q3" s="22"/>
-    </row>
-    <row r="4" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="37" t="s">
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H10" s="12">
         <v>2</v>
       </c>
-      <c r="C4" s="37"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="22"/>
-      <c r="M4" s="22"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="22"/>
-      <c r="P4" s="22"/>
-      <c r="Q4" s="22"/>
-    </row>
-    <row r="5" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="23"/>
-      <c r="B5" s="38" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="38"/>
-      <c r="K5" s="38"/>
-      <c r="L5" s="38"/>
-      <c r="M5" s="38"/>
-      <c r="N5" s="38"/>
-      <c r="O5" s="38"/>
-      <c r="P5" s="34"/>
-      <c r="Q5" s="24"/>
-    </row>
-    <row r="6" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
-      <c r="B6" s="38" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="38"/>
-      <c r="D6" s="38"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="38"/>
-      <c r="I6" s="38"/>
-      <c r="J6" s="38"/>
-      <c r="K6" s="38"/>
-      <c r="L6" s="38"/>
-      <c r="M6" s="38"/>
-      <c r="N6" s="38"/>
-      <c r="O6" s="38"/>
-      <c r="P6" s="34"/>
-      <c r="Q6" s="24"/>
-    </row>
-    <row r="7" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="25" t="s">
+      <c r="I10" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12">
+        <v>111.5</v>
+      </c>
+      <c r="L10" s="12">
+        <v>223</v>
+      </c>
+      <c r="M10" s="12">
+        <v>240</v>
+      </c>
+      <c r="N10" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="O10" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="P10" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q10" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="R10" s="32" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B11" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H11" s="12">
+        <v>2</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12">
+        <v>98</v>
+      </c>
+      <c r="L11" s="12">
+        <v>196</v>
+      </c>
+      <c r="M11" s="12">
+        <v>220</v>
+      </c>
+      <c r="N11" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="O11" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="P11" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q11" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="R11" s="32" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B12" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H12" s="12">
+        <v>2</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12">
+        <v>103.53</v>
+      </c>
+      <c r="L12" s="12">
+        <v>207.06</v>
+      </c>
+      <c r="M12" s="12">
+        <v>216</v>
+      </c>
+      <c r="N12" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="O12" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="P12" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q12" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="R12" s="32" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B13" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H13" s="12">
+        <v>2</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12">
+        <v>86.2</v>
+      </c>
+      <c r="L13" s="12">
+        <v>172.4</v>
+      </c>
+      <c r="M13" s="12">
+        <v>182</v>
+      </c>
+      <c r="N13" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="O13" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="P13" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q13" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="R13" s="27" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B14" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H14" s="12">
+        <v>2</v>
+      </c>
+      <c r="I14" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12">
+        <v>86.2</v>
+      </c>
+      <c r="L14" s="12">
+        <v>172.4</v>
+      </c>
+      <c r="M14" s="12">
+        <v>182</v>
+      </c>
+      <c r="N14" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="O14" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="P14" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q14" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="R14" s="27" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B15" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H15" s="12">
+        <v>2</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12">
+        <v>59</v>
+      </c>
+      <c r="L15" s="12">
+        <v>118</v>
+      </c>
+      <c r="M15" s="12">
+        <v>126</v>
+      </c>
+      <c r="N15" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="O15" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="P15" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q15" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="R15" s="27" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B16" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H16" s="12">
+        <v>2</v>
+      </c>
+      <c r="I16" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12">
+        <v>51.94</v>
+      </c>
+      <c r="L16" s="12">
+        <v>103.88</v>
+      </c>
+      <c r="M16" s="12">
+        <v>113</v>
+      </c>
+      <c r="N16" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="O16" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="P16" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q16" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="R16" s="30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B17" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H17" s="12">
+        <v>2</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12">
+        <v>56.2</v>
+      </c>
+      <c r="L17" s="12">
+        <v>112.4</v>
+      </c>
+      <c r="M17" s="12">
+        <v>122</v>
+      </c>
+      <c r="N17" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="O17" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="P17" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q17" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="R17" s="30" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="18" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B18" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H18" s="12">
+        <v>2</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="K18" s="13">
+        <v>52.07</v>
+      </c>
+      <c r="L18" s="13">
+        <v>104.14</v>
+      </c>
+      <c r="M18" s="13">
+        <v>114</v>
+      </c>
+      <c r="N18" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="O18" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="P18" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q18" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="R18" s="30" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B19" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H19" s="12">
+        <v>2</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="K19" s="13">
+        <v>32.299999999999997</v>
+      </c>
+      <c r="L19" s="13">
+        <v>64.599999999999994</v>
+      </c>
+      <c r="M19" s="13">
+        <v>76</v>
+      </c>
+      <c r="N19" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="O19" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="P19" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q19" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="R19" s="30" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B20" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H20" s="12">
+        <v>2</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="K20" s="13">
+        <v>29.8</v>
+      </c>
+      <c r="L20" s="13">
+        <v>59.6</v>
+      </c>
+      <c r="M20" s="13">
+        <v>68</v>
+      </c>
+      <c r="N20" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="O20" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="P20" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q20" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="R20" s="30" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B21" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H21" s="12">
         <v>5</v>
       </c>
-      <c r="B7" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="J7" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="K7" s="26" t="s">
+      <c r="I21" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="K21" s="13">
+        <v>20</v>
+      </c>
+      <c r="L21" s="13">
+        <v>100</v>
+      </c>
+      <c r="M21" s="13">
+        <v>112</v>
+      </c>
+      <c r="N21" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="L7" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="M7" s="26" t="s">
+      <c r="O21" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="P21" s="31" t="s">
         <v>97</v>
       </c>
-      <c r="N7" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="O7" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="P7" s="26" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q7" s="27" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="28" t="s">
+      <c r="Q21" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="R21" s="30" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="22" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B22" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="C22" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="28">
-        <v>500</v>
-      </c>
-      <c r="I8" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="J8" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="K8" s="29"/>
-      <c r="L8" s="29"/>
-      <c r="M8" s="29"/>
-      <c r="N8" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="O8" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="P8" s="29"/>
-      <c r="Q8" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="R8" s="31"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B9" s="13" t="s">
+      <c r="D22" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="F9" s="13" t="s">
+      <c r="E22" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H22" s="12">
+        <v>5</v>
+      </c>
+      <c r="I22" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="K22" s="13">
+        <v>26.9</v>
+      </c>
+      <c r="L22" s="13">
+        <v>134.51</v>
+      </c>
+      <c r="M22" s="13">
+        <v>150</v>
+      </c>
+      <c r="N22" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="O22" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="P22" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q22" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="R22" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="G9" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="H9" s="13">
-        <v>2</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13">
-        <v>899</v>
-      </c>
-      <c r="L9" s="13">
-        <v>1798</v>
-      </c>
-      <c r="M9" s="13">
-        <v>1850</v>
-      </c>
-      <c r="N9" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="O9" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="P9" s="40" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q9" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="R9" s="33" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B10" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="H10" s="13">
-        <v>8</v>
-      </c>
-      <c r="I10" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13">
-        <v>500</v>
-      </c>
-      <c r="L10" s="13">
-        <v>4000</v>
-      </c>
-      <c r="M10" s="13">
-        <v>4100</v>
-      </c>
-      <c r="N10" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="O10" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="P10" s="40" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q10" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="R10" s="33" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B11" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="H11" s="13">
-        <v>2</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13">
-        <v>111.5</v>
-      </c>
-      <c r="L11" s="13">
-        <v>223</v>
-      </c>
-      <c r="M11" s="13">
-        <v>240</v>
-      </c>
-      <c r="N11" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="O11" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="P11" s="40" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q11" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="R11" s="41" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B12" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="H12" s="13">
-        <v>2</v>
-      </c>
-      <c r="I12" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13">
-        <v>98</v>
-      </c>
-      <c r="L12" s="13">
-        <v>196</v>
-      </c>
-      <c r="M12" s="13">
-        <v>220</v>
-      </c>
-      <c r="N12" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="O12" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="P12" s="40" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q12" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="R12" s="41" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B13" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="H13" s="13">
-        <v>2</v>
-      </c>
-      <c r="I13" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13">
-        <v>103.53</v>
-      </c>
-      <c r="L13" s="13">
-        <v>207.06</v>
-      </c>
-      <c r="M13" s="13">
-        <v>216</v>
-      </c>
-      <c r="N13" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="O13" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="P13" s="40" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q13" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="R13" s="41" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B14" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="H14" s="13">
-        <v>2</v>
-      </c>
-      <c r="I14" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13">
-        <v>86.2</v>
-      </c>
-      <c r="L14" s="13">
-        <v>172.4</v>
-      </c>
-      <c r="M14" s="13">
-        <v>182</v>
-      </c>
-      <c r="N14" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="O14" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="P14" s="40" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q14" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="R14" s="32" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B15" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="H15" s="13">
-        <v>2</v>
-      </c>
-      <c r="I15" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13">
-        <v>86.2</v>
-      </c>
-      <c r="L15" s="13">
-        <v>172.4</v>
-      </c>
-      <c r="M15" s="13">
-        <v>182</v>
-      </c>
-      <c r="N15" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="O15" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="P15" s="40" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q15" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="R15" s="32" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B16" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="H16" s="13">
-        <v>2</v>
-      </c>
-      <c r="I16" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13">
-        <v>59</v>
-      </c>
-      <c r="L16" s="13">
-        <v>118</v>
-      </c>
-      <c r="M16" s="13">
-        <v>126</v>
-      </c>
-      <c r="N16" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="O16" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="P16" s="40" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q16" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="R16" s="32" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B17" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="H17" s="13">
-        <v>2</v>
-      </c>
-      <c r="I17" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13">
-        <v>51.94</v>
-      </c>
-      <c r="L17" s="13">
-        <v>103.88</v>
-      </c>
-      <c r="M17" s="13">
-        <v>113</v>
-      </c>
-      <c r="N17" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="O17" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="P17" s="40" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q17" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="R17" s="39" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B18" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="H18" s="13">
-        <v>2</v>
-      </c>
-      <c r="I18" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13">
-        <v>56.2</v>
-      </c>
-      <c r="L18" s="13">
-        <v>112.4</v>
-      </c>
-      <c r="M18" s="13">
-        <v>122</v>
-      </c>
-      <c r="N18" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="O18" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="P18" s="40" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q18" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="R18" s="39" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B19" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="F19" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="H19" s="13">
-        <v>2</v>
-      </c>
-      <c r="I19" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="K19" s="14">
-        <v>52.07</v>
-      </c>
-      <c r="L19" s="14">
-        <v>104.14</v>
-      </c>
-      <c r="M19" s="14">
-        <v>114</v>
-      </c>
-      <c r="N19" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="O19" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="P19" s="40" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q19" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="R19" s="39" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B20" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="F20" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="H20" s="13">
-        <v>2</v>
-      </c>
-      <c r="I20" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="K20" s="14">
-        <v>32.299999999999997</v>
-      </c>
-      <c r="L20" s="14">
-        <v>64.599999999999994</v>
-      </c>
-      <c r="M20" s="14">
-        <v>76</v>
-      </c>
-      <c r="N20" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="O20" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="P20" s="40" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q20" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="R20" s="39" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B21" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="F21" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="G21" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="H21" s="13">
-        <v>2</v>
-      </c>
-      <c r="I21" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="K21" s="14">
-        <v>29.8</v>
-      </c>
-      <c r="L21" s="14">
-        <v>59.6</v>
-      </c>
-      <c r="M21" s="14">
-        <v>68</v>
-      </c>
-      <c r="N21" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="O21" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="P21" s="40" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q21" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="R21" s="39" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B22" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="F22" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="H22" s="13">
-        <v>5</v>
-      </c>
-      <c r="I22" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="K22" s="14">
-        <v>20</v>
-      </c>
-      <c r="L22" s="14">
-        <v>100</v>
-      </c>
-      <c r="M22" s="14">
-        <v>112</v>
-      </c>
-      <c r="N22" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="O22" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="P22" s="40" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q22" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="R22" s="39" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B23" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="F23" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="G23" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="H23" s="13">
-        <v>5</v>
-      </c>
-      <c r="I23" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="K23" s="14">
-        <v>26.9</v>
-      </c>
-      <c r="L23" s="14">
-        <v>134.51</v>
-      </c>
-      <c r="M23" s="14">
-        <v>150</v>
-      </c>
-      <c r="N23" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="O23" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="P23" s="40" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q23" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="R23" s="39" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="R24" s="32"/>
-    </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="R25" s="32"/>
-    </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="R26" s="32"/>
-    </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="R27" s="32"/>
-    </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="R28" s="32"/>
+    </row>
+    <row r="23" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="R23" s="27"/>
+    </row>
+    <row r="24" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="R24" s="27"/>
+    </row>
+    <row r="25" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="R25" s="27"/>
+    </row>
+    <row r="26" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="R26" s="27"/>
+    </row>
+    <row r="27" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="R27" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3028,9 +2935,9 @@
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="R9" r:id="rId1" display="https://item.taobao.com/item.htm?abbucket=6&amp;id=1048993394353&amp;mi_id=0000EZWHscjiBdiz25LXscDcduExPTiJ3LaiwvRb889Q4kM&amp;ns=1&amp;priceTId=213e054c17873228014212574e0e7b&amp;spm=a21n57.1.hoverItem.3&amp;utparam=%7B%22aplus_abtest%22%3A%22ca043c936c0c464d91a736cfb57f836c%22%7D&amp;xxc=taobaoSearch" xr:uid="{F8F58A37-42D3-4B4A-85F3-CBF7E2ABCEDA}"/>
-    <hyperlink ref="R10" r:id="rId2" xr:uid="{6FE6ECF3-B10E-4967-B0E3-2442EE33CCA4}"/>
-    <hyperlink ref="R11" r:id="rId3" display="https://detail.tmall.com/item.htm?id=944470612837&amp;mi_id=00005O-lId5LKmOpPfOGBbEzVrmJhXIJpt6YGgmsKFyr3IY&amp;spm=tbpc.boughtlist.suborder_itemtitle.1.7f512e8dWmzysP" xr:uid="{6B757020-3852-4F8A-A2BE-67A97BE9C9B5}"/>
+    <hyperlink ref="R8" r:id="rId1" display="https://item.taobao.com/item.htm?abbucket=6&amp;id=1048993394353&amp;mi_id=0000EZWHscjiBdiz25LXscDcduExPTiJ3LaiwvRb889Q4kM&amp;ns=1&amp;priceTId=213e054c17873228014212574e0e7b&amp;spm=a21n57.1.hoverItem.3&amp;utparam=%7B%22aplus_abtest%22%3A%22ca043c936c0c464d91a736cfb57f836c%22%7D&amp;xxc=taobaoSearch" xr:uid="{F8F58A37-42D3-4B4A-85F3-CBF7E2ABCEDA}"/>
+    <hyperlink ref="R9" r:id="rId2" xr:uid="{6FE6ECF3-B10E-4967-B0E3-2442EE33CCA4}"/>
+    <hyperlink ref="R10" r:id="rId3" display="https://detail.tmall.com/item.htm?id=944470612837&amp;mi_id=00005O-lId5LKmOpPfOGBbEzVrmJhXIJpt6YGgmsKFyr3IY&amp;spm=tbpc.boughtlist.suborder_itemtitle.1.7f512e8dWmzysP" xr:uid="{6B757020-3852-4F8A-A2BE-67A97BE9C9B5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
@@ -3041,19 +2948,19 @@
           <x14:formula1>
             <xm:f>二级分类目录!$C$2:$G$2</xm:f>
           </x14:formula1>
-          <xm:sqref>C24:C1048576 C8:C10 D9:D10</xm:sqref>
+          <xm:sqref>C23:C1048576 C8:D9</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
           <x14:formula1>
             <xm:f>项目归属!$B$2:$B$8</xm:f>
           </x14:formula1>
-          <xm:sqref>E8:E10 E24:E1048576</xm:sqref>
+          <xm:sqref>E23:E1048576 E8:E9</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>二级分类目录!$A$2:$A$3</xm:f>
           </x14:formula1>
-          <xm:sqref>B8:B10 B24:B1048576</xm:sqref>
+          <xm:sqref>B23:B1048576 B8:B9</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3064,284 +2971,284 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" style="3" customWidth="1"/>
     <col min="2" max="2" width="15" style="3" customWidth="1"/>
-    <col min="3" max="3" width="21.44140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="21.4140625" style="3" customWidth="1"/>
     <col min="4" max="4" width="26" style="3" customWidth="1"/>
     <col min="5" max="5" width="15" style="3" customWidth="1"/>
-    <col min="6" max="6" width="23.77734375" style="3" customWidth="1"/>
-    <col min="7" max="7" width="8.44140625" style="3" customWidth="1"/>
-    <col min="8" max="16384" width="8.77734375" style="3"/>
+    <col min="6" max="6" width="23.75" style="3" customWidth="1"/>
+    <col min="7" max="7" width="8.4140625" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="8.75" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="2" customFormat="1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
     </row>
-    <row r="2" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="D3" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>44</v>
-      </c>
       <c r="G3" s="5"/>
     </row>
-    <row r="4" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
       <c r="B4" s="6" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="G4" s="5"/>
     </row>
-    <row r="5" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="6" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="G5" s="5"/>
     </row>
-    <row r="6" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="5" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="G6" s="5"/>
     </row>
-    <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="6" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G7" s="5"/>
     </row>
-    <row r="8" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="6" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="9" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="G8" s="5"/>
     </row>
-    <row r="9" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="6" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="9" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="G9" s="5"/>
     </row>
-    <row r="10" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="6" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="G10" s="5"/>
     </row>
-    <row r="11" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="6" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G11" s="5"/>
     </row>
-    <row r="12" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="6" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
       <c r="F12" s="6" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G12" s="5"/>
     </row>
-    <row r="13" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="6" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="G13" s="5"/>
     </row>
-    <row r="14" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="6" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
       <c r="F14" s="6" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="G14" s="5"/>
     </row>
-    <row r="15" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="6" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="G15" s="5"/>
     </row>
-    <row r="16" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="10" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
       <c r="G16" s="5"/>
     </row>
-    <row r="17" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="10" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
       <c r="G17" s="5"/>
     </row>
-    <row r="18" spans="1:7" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="10" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
@@ -3356,12 +3263,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30.77734375" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.77734375" style="1"/>
+    <col min="2" max="2" width="30.75" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.75" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -3371,32 +3278,37 @@
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>83</v>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
